--- a/data/processed/existencias_procesado.xlsx
+++ b/data/processed/existencias_procesado.xlsx
@@ -606,12 +606,12 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLA-15  </t>
+          <t xml:space="preserve">AU107   </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KG.MACRO ANCHO 230mm MI40 GENERICO NEGRO 50 CM  </t>
+          <t xml:space="preserve">BOLSAS PLASTICO IMPR.HUESO 45*80 G-300 PE-TR    </t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -623,103 +623,107 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>275</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="n">
-        <v>267.106</v>
+        <v>683</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>317</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>3000</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>51754</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>267.106</v>
+        <v>3683</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>400000174</t>
+          <t>400000442</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>275</v>
+        <v>1000</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MACROMUR 174</t>
+          <t>PLASTICO AGUILAR 442</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="b">
         <v>1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>400000174</t>
+          <t>400000442</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GRAFIMOL</t>
+          <t>J.AGUILAR</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>174</v>
+        <v>442</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.856472727272727</v>
+        <v>9.757142857142858</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-0.3520157325467059</v>
+        <v>-0.7207472959685348</v>
       </c>
       <c r="AG2" t="n">
-        <v>-7.894000000000005</v>
+        <v>2683</v>
       </c>
       <c r="AH2" s="1" t="n">
-        <v>46144.99530909091</v>
+        <v>46507.3</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FA-10   </t>
+          <t xml:space="preserve">HA-1002 </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CULARES CAL.60/65 ATA/HILO ROJO BIDON 1000 P/   </t>
+          <t xml:space="preserve">PIEZAS FRO RECTO 75*115 HILO BLANCO             </t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>718.27</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -727,43 +731,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="n">
-        <v>314.584</v>
+        <v>9630.338</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>5369</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>51613</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>4314.584</v>
+        <v>15630.338</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>400001066</t>
+          <t>410000002</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="T3" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
@@ -772,60 +776,62 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>FAMILIA RUIZ 1066</t>
+          <t>FIBRAN 870</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="b">
         <v>1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>400001066</t>
+          <t>410000002</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>VAN HESSEN</t>
+          <t>VAESSEN</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>1066</v>
+        <v>10000002</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2097226666666667</v>
+        <v>6.420225333333333</v>
       </c>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>-1.088351177133947</v>
+      </c>
       <c r="AG3" t="n">
-        <v>3314.584</v>
+        <v>630.3379999999997</v>
       </c>
       <c r="AH3" s="1" t="n">
-        <v>46131.13472533333</v>
+        <v>46211.94157733333</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1004 </t>
+          <t xml:space="preserve">HA-1003 </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTS.DE CURVADO PLISADO S1 CAL 36 1440 M/        </t>
+          <t xml:space="preserve">PIEZAS FIBROSA HILO ROJO 71*55 S 1000P/CAJA     </t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3239.61</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -833,32 +839,32 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>125000</v>
+        <v>45000</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>120000</v>
+        <v>42000</v>
       </c>
       <c r="I4" t="n">
-        <v>17680.764</v>
+        <v>18825.73</v>
       </c>
       <c r="J4" t="n">
-        <v>102319</v>
+        <v>23174</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>85050</v>
+        <v>24000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>51529</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>102730.764</v>
+        <v>42825.73</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -866,14 +872,14 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>120000</v>
+        <v>42000</v>
       </c>
       <c r="T4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>11500</v>
+        <v>4400</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
@@ -882,7 +888,7 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="b">
         <v>1</v>
@@ -901,70 +907,72 @@
         <v>870</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.537457739130435</v>
+        <v>4.278575</v>
       </c>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>-0.3581881769719195</v>
+      </c>
       <c r="AG4" t="n">
-        <v>-17269.236</v>
+        <v>825.7300000000032</v>
       </c>
       <c r="AH4" s="1" t="n">
-        <v>46173.53176939131</v>
+        <v>46207.13184318181</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1045 </t>
+          <t xml:space="preserve">HA-1004 </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTS.PLISADO RECTO CALIBRE 50                    </t>
+          <t xml:space="preserve">MTS.DE CURVADO PLISADO S1 CAL 36 1440 M/        </t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8456.549999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50000</v>
+        <v>125000</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>48000</v>
+        <v>120000</v>
       </c>
       <c r="I5" t="n">
-        <v>38682.129</v>
+        <v>71631.20699999999</v>
       </c>
       <c r="J5" t="n">
-        <v>9317</v>
+        <v>48368</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>20160</v>
+        <v>56700</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>51335</t>
+          <t>51806</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>58842.129</v>
+        <v>128331.207</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -972,14 +980,14 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>48000</v>
+        <v>120000</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>4800</v>
+        <v>11500</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
@@ -988,7 +996,7 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
@@ -1007,37 +1015,39 @@
         <v>870</v>
       </c>
       <c r="AD5" t="n">
-        <v>8.058776875</v>
+        <v>6.228800608695652</v>
       </c>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>-0.3598926276081855</v>
+      </c>
       <c r="AG5" t="n">
-        <v>10842.129</v>
+        <v>8331.206999999995</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>46196.811438125</v>
+        <v>46217.11464773913</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AU136   </t>
+          <t xml:space="preserve">HA-1043 </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIBON REF.3910 55mmX800m CAJA 20 ROLLOS         </t>
+          <t xml:space="preserve">MADEJAS CALIBRE 80 CALIDAD L                    </t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.61</v>
+        <v>1207.09</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1045,215 +1055,215 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>14000</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>13000</v>
       </c>
       <c r="I6" t="n">
-        <v>19.129</v>
+        <v>7170.92</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>5829</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>40</v>
+        <v>12000</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>51672</t>
+          <t>51628</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>59.129</v>
+        <v>19170.92</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>400000063</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>13000</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>1400</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>IMPREMUR 1198</t>
+          <t>FIBRAN 870</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="b">
         <v>1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>400000063</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>LARA GRANADA</t>
+          <t>FIBRAN</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>63</v>
+        <v>870</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.78225</v>
+        <v>5.122085714285714</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>-0.5325670498084292</v>
+        <v>-0.1598140983688043</v>
       </c>
       <c r="AG6" t="n">
-        <v>34.129</v>
+        <v>6170.919999999998</v>
       </c>
       <c r="AH6" s="1" t="n">
-        <v>46214.47575</v>
+        <v>46234.8546</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-10    </t>
+          <t xml:space="preserve">HA-1005 </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAJAS CARTON MODELO 10                          </t>
+          <t xml:space="preserve">MTS.DE CURVADO PLISADO S1 CAL.32 1815 M/CAJA    </t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>774.84</v>
+        <v>4952.22</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4000</v>
+        <v>46000</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>3500</v>
+        <v>45000</v>
       </c>
       <c r="I7" t="n">
-        <v>2513.723</v>
+        <v>31578.67</v>
       </c>
       <c r="J7" t="n">
-        <v>986</v>
+        <v>13421</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>5000</v>
+        <v>22680</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>51757</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>7513.723</v>
+        <v>54258.67</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>400001057</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>3500</v>
+        <v>45000</v>
       </c>
       <c r="T7" t="n">
-        <v>4000</v>
+        <v>12</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>1100</v>
+        <v>4300</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>SAECO 1057</t>
+          <t>FIBRAN 870</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="b">
         <v>1</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>400001057</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>SAECO</t>
+          <t>FIBRAN</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>1057</v>
+        <v>870</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.285202727272727</v>
+        <v>7.343876744186046</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>-0.4196479273140261</v>
+        <v>0.1317025495636301</v>
       </c>
       <c r="AG7" t="n">
-        <v>4013.723</v>
+        <v>9258.669999999998</v>
       </c>
       <c r="AH7" s="1" t="n">
-        <v>46158.81460090909</v>
+        <v>46227.32806744186</v>
       </c>
       <c r="AI7" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-29    </t>
+          <t xml:space="preserve">AU153   </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAJAS CARTON MODELO 29                          </t>
+          <t xml:space="preserve">MTS.PLISADO EDC 34 EDICAS NB                    </t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2582.79</v>
+        <v>1704.94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1268,84 +1278,84 @@
         <v>14000</v>
       </c>
       <c r="I8" t="n">
-        <v>8866.875</v>
+        <v>10535.344</v>
       </c>
       <c r="J8" t="n">
-        <v>5133</v>
+        <v>3464</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>22000</v>
+        <v>12060</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>30866.875</v>
+        <v>22595.344</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>400001057</t>
+          <t>400000921</t>
         </is>
       </c>
       <c r="S8" t="n">
         <v>14000</v>
       </c>
       <c r="T8" t="n">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>4200</v>
+        <v>1600</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>SAECO 1057</t>
+          <t>EDICAS 921</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Z8" t="b">
         <v>1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>400001057</t>
+          <t>400000921</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>SAECO</t>
+          <t>EDIBLE</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>1057</v>
+        <v>921</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.111160714285715</v>
+        <v>6.584589999999999</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>-0.6261484673550695</v>
+        <v>0.06155055309864277</v>
       </c>
       <c r="AG8" t="n">
-        <v>16866.875</v>
+        <v>8595.344000000001</v>
       </c>
       <c r="AH8" s="1" t="n">
-        <v>46162.44479166667</v>
+        <v>46237.85463</v>
       </c>
       <c r="AI8" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1361,7 +1371,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3224.5</v>
+        <v>974.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1376,10 +1386,10 @@
         <v>28000</v>
       </c>
       <c r="I9" t="n">
-        <v>20492.92</v>
+        <v>13184.263</v>
       </c>
       <c r="J9" t="n">
-        <v>7507</v>
+        <v>14815</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1394,7 +1404,7 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>55492.92</v>
+        <v>48184.263</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1437,39 +1447,39 @@
         <v>1144</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.855119999999999</v>
+        <v>3.766932285714286</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>-0.08543960303923082</v>
+        <v>-2.590848466194726</v>
       </c>
       <c r="AG9" t="n">
-        <v>27492.92</v>
+        <v>20184.263</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>46221.98584</v>
+        <v>46235.368526</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-27    </t>
+          <t xml:space="preserve">CG-61   </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAJAS CARTON MODELO 27                          </t>
+          <t xml:space="preserve">ETIQUETA BACON AHUMADO                          </t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2169.84</v>
+        <v>390.98</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1477,103 +1487,103 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="I10" t="n">
-        <v>10002.117</v>
+        <v>8231.768</v>
       </c>
       <c r="J10" t="n">
-        <v>997</v>
+        <v>1768</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>51701</t>
+          <t>51803</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>20002.117</v>
+        <v>33231.768</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>400001108</t>
+          <t>400001111</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="T10" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>SAECO 1057</t>
+          <t>INDULABEL 1111</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z10" t="b">
         <v>1</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>400001108</t>
+          <t>400001111</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>XUBER</t>
+          <t>INDULABEL</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.334039</v>
+        <v>5.144855</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>-0.3825904214135603</v>
+        <v>-3.092280935086193</v>
       </c>
       <c r="AG10" t="n">
-        <v>9002.116999999998</v>
+        <v>23231.768</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>46157.67160633334</v>
+        <v>46284.388985</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1005 </t>
+          <t xml:space="preserve">CG-95   </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTS.DE CURVADO PLISADO S1 CAL.32 1815 M/CAJA    </t>
+          <t xml:space="preserve">ETIQ.PP BLANCO LOMO EMBUCHADO MEDIO 70x150      </t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1581,111 +1591,111 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>46000</v>
+        <v>40000</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="I11" t="n">
-        <v>25027.764</v>
+        <v>12361.191</v>
       </c>
       <c r="J11" t="n">
-        <v>19972</v>
+        <v>5638</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>22680</v>
+        <v>25000</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>51755</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>47707.764</v>
+        <v>37361.191</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400001235</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="T11" t="n">
-        <v>12</v>
+        <v>20000</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>4300</v>
+        <v>2500</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>FIBRAN 870</t>
+          <t>GRAFI  538/INDU 1111</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="b">
         <v>1</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400001235</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>FIBRAN</t>
+          <t>GRAFIMUR 2</t>
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>870</v>
+        <v>1235</v>
       </c>
       <c r="AD11" t="n">
-        <v>5.82041023255814</v>
+        <v>4.9444764</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>-0.7365949008727397</v>
+        <v>-0.009648198181825496</v>
       </c>
       <c r="AG11" t="n">
-        <v>2707.764000000003</v>
+        <v>19361.191</v>
       </c>
       <c r="AH11" s="1" t="n">
-        <v>46188.66380186046</v>
+        <v>46243.6113348</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-34    </t>
+          <t xml:space="preserve">HA-1039 </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAJAS CARTON MODELO 34 FUET                     </t>
+          <t xml:space="preserve">MTS.PLISADO RECTA S1 CAL.45 MCH FRIBROSA        </t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2401.99</v>
+        <v>604.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1693,140 +1703,140 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>9500</v>
+        <v>12500</v>
       </c>
       <c r="I12" t="n">
-        <v>6869.462</v>
+        <v>11099.98</v>
       </c>
       <c r="J12" t="n">
-        <v>2630</v>
+        <v>1400</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>18000</v>
+        <v>8750</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>24869.462</v>
+        <v>19849.98</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>400001108</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>9500</v>
+        <v>12500</v>
       </c>
       <c r="T12" t="n">
-        <v>10000</v>
+        <v>6</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>SAECO 1057</t>
+          <t>FIBRAN 870</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Z12" t="b">
         <v>1</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>400001108</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>XUBER</t>
+          <t>FIBRAN</t>
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>1108</v>
+        <v>870</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.289820666666667</v>
+        <v>9.249983333333333</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>-0.2489644003513753</v>
+        <v>-0.9857686579513487</v>
       </c>
       <c r="AG12" t="n">
-        <v>15369.462</v>
+        <v>7349.98</v>
       </c>
       <c r="AH12" s="1" t="n">
-        <v>46169.02874466667</v>
+        <v>46254.79155</v>
       </c>
       <c r="AI12" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH-17   </t>
+          <t xml:space="preserve">HA-1045 </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIBRU SECURE 88 BLANCO PIEZA 65 ctm             </t>
+          <t xml:space="preserve">MTS.PLISADO RECTO CALIBRE 50                    </t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3397.48</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6000</v>
+        <v>50000</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>5500</v>
+        <v>48000</v>
       </c>
       <c r="I13" t="n">
-        <v>3511.466</v>
+        <v>43504.966</v>
       </c>
       <c r="J13" t="n">
-        <v>1988</v>
+        <v>4495</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>5000</v>
+        <v>20160</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>51440</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
-        <v>8511.466</v>
+        <v>63664.966</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1834,14 +1844,14 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>5500</v>
+        <v>48000</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>450</v>
+        <v>4800</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
@@ -1869,153 +1879,165 @@
         <v>870</v>
       </c>
       <c r="AD13" t="n">
-        <v>7.803257777777778</v>
+        <v>9.063534583333334</v>
       </c>
       <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>-0.4128118487820385</v>
+      </c>
       <c r="AG13" t="n">
-        <v>3011.466</v>
+        <v>15664.966</v>
       </c>
       <c r="AH13" s="1" t="n">
-        <v>46243.40058222222</v>
+        <v>46231.84474208333</v>
       </c>
       <c r="AI13" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLA-10  </t>
+          <t xml:space="preserve">PH-17   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">KG.LAMINA COMPLEJO A 230mm 40my ANONIMA         </t>
+          <t xml:space="preserve">FIBRU SECURE 88 BLANCO PIEZA 65 ctm             </t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>416.75</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>150</v>
+        <v>5500</v>
       </c>
       <c r="I14" t="n">
-        <v>56.153</v>
+        <v>3661.847</v>
       </c>
       <c r="J14" t="n">
-        <v>93</v>
+        <v>1838</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>51440</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>256.153</v>
+        <v>8661.847</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>400000174</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>150</v>
+        <v>5500</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>FIBRAN 870</t>
+        </is>
+      </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>400000174</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>GRAFIMOL</t>
+          <t>FIBRAN</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>174</v>
-      </c>
-      <c r="AD14" t="inlineStr"/>
+        <v>870</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>8.137437777777778</v>
+      </c>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>-0.07978404319136168</v>
+      </c>
       <c r="AG14" t="n">
-        <v>106.153</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>3161.847</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>46273.73984222222</v>
+      </c>
       <c r="AI14" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH-37   </t>
+          <t xml:space="preserve">RR-30   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROLAN V-2000 CALIBRE 200 BLANCO PLISADO        </t>
+          <t xml:space="preserve">METROS DE TUBO 178 TRANSPARENTE BOBINA          </t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1162.18</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5000</v>
+        <v>23500</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="I15" t="n">
-        <v>1573.627</v>
+        <v>29661.222</v>
       </c>
       <c r="J15" t="n">
-        <v>1426</v>
+        <v>338</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -2030,76 +2052,78 @@
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>6573.627</v>
+        <v>29661.222</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>400000068</t>
+          <t>400000908</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="T15" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>310</v>
+        <v>2000</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>PHH  68</t>
+          <t>FIBRACO   908</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="b">
         <v>1</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>400000068</t>
+          <t>400000908</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>PHH</t>
+          <t>FIBRACO</t>
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>68</v>
+        <v>908</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.076216129032258</v>
+        <v>14.830611</v>
       </c>
       <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>-0.7209038186855736</v>
+      </c>
       <c r="AG15" t="n">
-        <v>3573.627</v>
+        <v>-338.7779999999984</v>
       </c>
       <c r="AH15" s="1" t="n">
-        <v>46259.43673870968</v>
+        <v>46242.814277</v>
       </c>
       <c r="AI15" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1037 </t>
+          <t xml:space="preserve">ED-11   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PIEZAS COSIDAS CAL.95*65 1000 P/CAJA            </t>
+          <t xml:space="preserve">MTS.PLISADO CAL.21 EDICAS NU                    </t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2107,127 +2131,127 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="I16" t="n">
-        <v>7658.933</v>
+        <v>4553.744</v>
       </c>
       <c r="J16" t="n">
-        <v>1341</v>
+        <v>1446</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>7000</v>
+        <v>16200</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>14658.933</v>
+        <v>20753.744</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>400001021</t>
+          <t>400000921</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>PERE TEIXIDOR 1021</t>
+          <t>EDICAS 921</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z16" t="b">
         <v>1</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>400001021</t>
+          <t>400000921</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>PERE TEIXIDOR</t>
+          <t>EDIBLE</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>1021</v>
+        <v>921</v>
       </c>
       <c r="AD16" t="n">
-        <v>7.658933</v>
+        <v>6.505348571428571</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
-        <v>5658.933000000001</v>
+        <v>14753.744</v>
       </c>
       <c r="AH16" s="1" t="n">
-        <v>46213.612531</v>
+        <v>46346.53744</v>
       </c>
       <c r="AI16" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH-21   </t>
+          <t xml:space="preserve">GR-28   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTS FILM TAPA TERMOFORMADO ANCHO 302mm 100 MI   </t>
+          <t xml:space="preserve">ENVUELTAS SALCHICHON PAVO CARCHELEJO HALAL      </t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4158.35</v>
+        <v>1614.51</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="I17" t="n">
-        <v>29666.441</v>
+        <v>9209.343000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>5333</v>
+        <v>790</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -2242,78 +2266,78 @@
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>79666.44100000001</v>
+        <v>9209.343000000001</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>400001232</t>
+          <t>400000174</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="T17" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>5100</v>
+        <v>1300</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>PHH  68</t>
+          <t>MACROMUR 174</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="b">
         <v>1</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>400001232</t>
+          <t>400000174</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>OTACI PACK</t>
+          <t>GRAFIMOL</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1232</v>
+        <v>174</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.816949215686274</v>
+        <v>7.084110000000001</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>-0.226447990188416</v>
+        <v>0.1948021381100148</v>
       </c>
       <c r="AG17" t="n">
-        <v>44666.44100000001</v>
+        <v>-790.6569999999992</v>
       </c>
       <c r="AH17" s="1" t="n">
-        <v>46220.3460954902</v>
+        <v>46188.58877</v>
       </c>
       <c r="AI17" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PH-32   </t>
+          <t xml:space="preserve">HA-1047 </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTS.PROLAN V-6 HGB/3 175 TRANSPARENTE PLISADO   </t>
+          <t xml:space="preserve">FIBROSA 075 MCH PLISADA METROS                  </t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2321,7 +2345,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2329,103 +2353,103 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="I18" t="n">
-        <v>2629.695</v>
+        <v>897.722</v>
       </c>
       <c r="J18" t="n">
-        <v>1370</v>
+        <v>102</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>51756</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>12629.695</v>
+        <v>1397.722</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>400000068</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="n">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>PHH  68</t>
+          <t>FIBRAN 870</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="b">
         <v>1</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>400000068</t>
+          <t>400000870</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>PHH</t>
+          <t>FIBRAN</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>68</v>
+        <v>870</v>
       </c>
       <c r="AD18" t="n">
-        <v>7.513414285714286</v>
+        <v>22.44305</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>-0.7542101042502003</v>
+        <v>0.7995188452285485</v>
       </c>
       <c r="AG18" t="n">
-        <v>8629.695</v>
+        <v>397.722</v>
       </c>
       <c r="AH18" s="1" t="n">
-        <v>46363.5939</v>
+        <v>46383.60135</v>
       </c>
       <c r="AI18" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1039 </t>
+          <t xml:space="preserve">PH-32   </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTS.PLISADO RECTA S1 CAL.45 MCH FRIBROSA        </t>
+          <t xml:space="preserve">MTS.PROLAN V-6 HGB/3 175 TRANSPARENTE PLISADO   </t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1002.14</v>
+        <v>199.52</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -2433,107 +2457,107 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>12500</v>
+        <v>4000</v>
       </c>
       <c r="I19" t="n">
-        <v>3475.26</v>
+        <v>1655.87</v>
       </c>
       <c r="J19" t="n">
-        <v>9024</v>
+        <v>2344</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>51460</t>
+          <t>51367</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>10975.26</v>
+        <v>11655.87</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400000068</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>12500</v>
+        <v>4000</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>10000</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>FIBRAN 870</t>
+          <t>PHH  68</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="b">
         <v>1</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400000068</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>FIBRAN</t>
+          <t>PHH</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>870</v>
+        <v>68</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.89605</v>
+        <v>4.731057142857143</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>-0.1974374837847008</v>
+        <v>-0.7542101042502003</v>
       </c>
       <c r="AG19" t="n">
-        <v>-1524.74</v>
+        <v>7655.870000000001</v>
       </c>
       <c r="AH19" s="1" t="n">
-        <v>46175.02235</v>
+        <v>46372.1174</v>
       </c>
       <c r="AI19" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AU168   </t>
+          <t xml:space="preserve">PH-38   </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FILM FONDO SKIN 441 mm 250 MICRAS               </t>
+          <t xml:space="preserve">MTS.TUBO 110 BLANCO PLISADO                     </t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2075.05</v>
+        <v>365.26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2541,211 +2565,211 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>40000</v>
+        <v>5500</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="I20" t="n">
-        <v>15036.57</v>
+        <v>4163.272</v>
       </c>
       <c r="J20" t="n">
-        <v>9963</v>
+        <v>836</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>51561</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>40036.57</v>
+        <v>9163.272000000001</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>400001156</t>
+          <t>400000908</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="T20" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>4000</v>
+        <v>460</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>W.HOFMANN  995 EVERTIS 1156</t>
+          <t>FIBRACO   908</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="b">
         <v>1</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>400001156</t>
+          <t>400000908</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>EVERTIS</t>
+          <t>FIBRACO</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>1156</v>
+        <v>908</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.7591425</v>
+        <v>9.050591304347826</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>-0.9276643936290689</v>
+        <v>-0.2593768822208837</v>
       </c>
       <c r="AG20" t="n">
-        <v>15036.57</v>
+        <v>4163.272000000001</v>
       </c>
       <c r="AH20" s="1" t="n">
-        <v>46181.0639975</v>
+        <v>46278.44109565218</v>
       </c>
       <c r="AI20" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CG-76   </t>
+          <t xml:space="preserve">PH-44   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETIQ.BLANCAS PAPEL COUCHE 100x55                </t>
+          <t xml:space="preserve">PROLAN V-6-2 REG 150mm Tint Bright Blue         </t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15241.86</v>
+        <v>62.81</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>150000</v>
+        <v>5000</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>130000</v>
+        <v>3000</v>
       </c>
       <c r="I21" t="n">
-        <v>101479.394</v>
+        <v>2668.245</v>
       </c>
       <c r="J21" t="n">
-        <v>28520</v>
+        <v>331</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>51673</t>
+          <t>51778</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>251479.394</v>
+        <v>12668.245</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>400001235</t>
+          <t>400000068</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>130000</v>
+        <v>3000</v>
       </c>
       <c r="T21" t="n">
-        <v>150000</v>
+        <v>10000</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>21000</v>
+        <v>170</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>INDULABEL 1111</t>
+          <t>PHH  68</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="b">
         <v>1</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>400001235</t>
+          <t>400000068</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>GRAFIMUR 2</t>
+          <t>PHH</t>
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>1235</v>
+        <v>68</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.832352095238095</v>
+        <v>15.69555882352941</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>-0.3777846010919927</v>
+        <v>-1.706575386085018</v>
       </c>
       <c r="AG21" t="n">
-        <v>121479.394</v>
+        <v>9668.245000000001</v>
       </c>
       <c r="AH21" s="1" t="n">
-        <v>46194.82646466666</v>
+        <v>46660.63361764706</v>
       </c>
       <c r="AI21" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1001 </t>
+          <t xml:space="preserve">PH-49   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">PIEZAS HILO ROJO 80*55 CMS 2000 P/CAJA          </t>
+          <t xml:space="preserve">FILM TAPA IMPRESA FLEXIBLE A 468mm              </t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2753,109 +2777,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>30000</v>
+        <v>5500</v>
       </c>
       <c r="I22" t="n">
-        <v>23208.746</v>
+        <v>2898.078</v>
       </c>
       <c r="J22" t="n">
-        <v>6791</v>
+        <v>2601</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>24000</v>
+        <v>7000</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>51474</t>
+          <t>51553</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>47208.746</v>
+        <v>9898.078</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400000995</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>30000</v>
+        <v>5500</v>
       </c>
       <c r="T22" t="n">
-        <v>12</v>
+        <v>15000</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>2400</v>
+        <v>350</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>FIBRAN 870</t>
+          <t>W.HOFMANN  995</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z22" t="b">
         <v>1</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400000995</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>FIBRAN</t>
+          <t>W.HOFMANN</t>
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>870</v>
+        <v>995</v>
       </c>
       <c r="AD22" t="n">
-        <v>9.670310833333334</v>
+        <v>8.280222857142856</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="n">
-        <v>17208.746</v>
+        <v>4398.078</v>
       </c>
       <c r="AH22" s="1" t="n">
-        <v>46248.69217583333</v>
+        <v>46336.96156</v>
       </c>
       <c r="AI22" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ22" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HA-1003 </t>
+          <t xml:space="preserve">PLA-15  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PIEZAS FIBROSA HILO ROJO 71*55 S 1000P/CAJA     </t>
+          <t xml:space="preserve">KG.MACRO ANCHO 230mm MI40 GENERICO NEGRO 50 CM  </t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>24.78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2863,89 +2887,91 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>45000</v>
+        <v>400</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>42000</v>
+        <v>275</v>
       </c>
       <c r="I23" t="n">
-        <v>21964.35</v>
+        <v>114.186</v>
       </c>
       <c r="J23" t="n">
-        <v>20035</v>
+        <v>160</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>24000</v>
+        <v>400</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>51614</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>45964.35</v>
+        <v>514.186</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400000174</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>42000</v>
+        <v>275</v>
       </c>
       <c r="T23" t="n">
-        <v>12</v>
+        <v>400</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>4400</v>
+        <v>55</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>FIBRAN 870</t>
+          <t>MACROMUR 174</t>
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="b">
         <v>1</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>400000870</t>
+          <t>400000174</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>FIBRAN</t>
+          <t>GRAFIMOL</t>
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>870</v>
+        <v>174</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.991897727272727</v>
+        <v>2.076109090909091</v>
       </c>
       <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
+      <c r="AF23" t="n">
+        <v>-1.21953188054883</v>
+      </c>
       <c r="AG23" t="n">
-        <v>3964.349999999999</v>
+        <v>239.186</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>46184.12510227273</v>
+        <v>46204.44185454545</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -3047,13 +3073,13 @@
         <v>14673.012</v>
       </c>
       <c r="AH24" s="1" t="n">
-        <v>46174.22019709092</v>
+        <v>46202.22019709092</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -3155,13 +3181,13 @@
         <v>5539.258</v>
       </c>
       <c r="AH25" s="1" t="n">
-        <v>46331.78516</v>
+        <v>46359.78516</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -3261,13 +3287,13 @@
         <v>7900.871999999999</v>
       </c>
       <c r="AH26" s="1" t="n">
-        <v>46311.68023111111</v>
+        <v>46339.68023111111</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -3367,13 +3393,13 @@
         <v>3575.17</v>
       </c>
       <c r="AH27" s="1" t="n">
-        <v>46206.02619</v>
+        <v>46234.02619</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ27" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -3473,13 +3499,13 @@
         <v>4035.617999999999</v>
       </c>
       <c r="AH28" s="1" t="n">
-        <v>46199.832884</v>
+        <v>46227.832884</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -3579,13 +3605,13 @@
         <v>10312.112</v>
       </c>
       <c r="AH29" s="1" t="n">
-        <v>46227.56056</v>
+        <v>46255.56056</v>
       </c>
       <c r="AI29" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -3685,13 +3711,13 @@
         <v>1134.84</v>
       </c>
       <c r="AH30" s="1" t="n">
-        <v>46400.4388</v>
+        <v>46428.4388</v>
       </c>
       <c r="AI30" s="1" t="n">
-        <v>46111</v>
+        <v>46139</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
